--- a/TJX.xlsx
+++ b/TJX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F2507A-6367-4465-810B-2F69E4E239A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1525F2-E059-49A4-8200-C010C0411EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{03FABE92-8095-40C1-84A9-F723AD2E6BD9}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{03FABE92-8095-40C1-84A9-F723AD2E6BD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1205,14 +1205,14 @@
     <xf numFmtId="2" fontId="13" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="169" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1238,15 +1238,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>15875</xdr:colOff>
+      <xdr:colOff>606425</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>34925</xdr:colOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>15875</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>109537</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1261,8 +1261,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12846050" y="128587"/>
-          <a:ext cx="19050" cy="8743950"/>
+          <a:off x="15265400" y="95250"/>
+          <a:ext cx="19050" cy="6943725"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1633,7 +1633,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="2">
-        <v>152.19999999999999</v>
+        <v>159.05000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1646,8 +1646,8 @@
       <c r="I4" s="3">
         <v>1126</v>
       </c>
-      <c r="J4" s="62" t="s">
-        <v>244</v>
+      <c r="J4" s="64" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="I5" s="6">
         <f>I4*I3</f>
-        <v>171377.19999999998</v>
+        <v>179090.30000000002</v>
       </c>
       <c r="J5" s="4"/>
     </row>
@@ -1668,10 +1668,10 @@
         <v>4</v>
       </c>
       <c r="I6" s="6">
-        <v>4640</v>
-      </c>
-      <c r="J6" s="62" t="s">
-        <v>244</v>
+        <v>6230</v>
+      </c>
+      <c r="J6" s="64" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1682,11 +1682,11 @@
         <v>5</v>
       </c>
       <c r="I7" s="6">
-        <f>1870+999</f>
+        <f>999+1870</f>
         <v>2869</v>
       </c>
-      <c r="J7" s="62" t="s">
-        <v>244</v>
+      <c r="J7" s="64" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="I8" s="6">
         <f>I5-I6+I7</f>
-        <v>169606.19999999998</v>
+        <v>175729.30000000002</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -2053,40 +2053,40 @@
         <v>2665</v>
       </c>
       <c r="W4" s="3">
-        <f t="shared" ref="W4:Y4" si="0">V4*1.03</f>
-        <v>2744.9500000000003</v>
+        <f>1348+1255+111</f>
+        <v>2714</v>
       </c>
       <c r="X4" s="3">
-        <f t="shared" si="0"/>
-        <v>2827.2985000000003</v>
+        <f t="shared" ref="W4:Y4" si="0">W4*1.03</f>
+        <v>2795.42</v>
       </c>
       <c r="Y4" s="3">
         <f t="shared" si="0"/>
-        <v>2912.1174550000005</v>
+        <v>2879.2826</v>
       </c>
       <c r="Z4" s="3">
         <f>Y4*1.03</f>
-        <v>2999.4809786500005</v>
+        <v>2965.6610780000001</v>
       </c>
       <c r="AA4" s="3">
         <f>Z4*1.02855</f>
-        <v>3085.1161605904581</v>
+        <v>3050.3307017769002</v>
       </c>
       <c r="AB4" s="3">
         <f>AA4</f>
-        <v>3085.1161605904581</v>
+        <v>3050.3307017769002</v>
       </c>
       <c r="AC4" s="3">
         <f t="shared" ref="AC4:AE4" si="1">AB4</f>
-        <v>3085.1161605904581</v>
+        <v>3050.3307017769002</v>
       </c>
       <c r="AD4" s="3">
         <f t="shared" si="1"/>
-        <v>3085.1161605904581</v>
+        <v>3050.3307017769002</v>
       </c>
       <c r="AE4" s="3">
         <f t="shared" si="1"/>
-        <v>3085.1161605904581</v>
+        <v>3050.3307017769002</v>
       </c>
       <c r="AF4" s="3">
         <v>3000</v>
@@ -2161,40 +2161,40 @@
         <v>1156</v>
       </c>
       <c r="W5" s="3">
-        <f t="shared" ref="W5:AC5" si="2">V5*1.055</f>
-        <v>1219.58</v>
+        <f>963+145+79</f>
+        <v>1187</v>
       </c>
       <c r="X5" s="3">
-        <f t="shared" si="2"/>
-        <v>1286.6569</v>
+        <f t="shared" ref="W5:AC5" si="2">W5*1.055</f>
+        <v>1252.2849999999999</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" si="2"/>
-        <v>1357.4230294999998</v>
+        <v>1321.1606749999999</v>
       </c>
       <c r="Z5" s="3">
         <f t="shared" si="2"/>
-        <v>1432.0812961224997</v>
+        <v>1393.8245121249997</v>
       </c>
       <c r="AA5" s="3">
         <f t="shared" si="2"/>
-        <v>1510.8457674092372</v>
+        <v>1470.4848602918746</v>
       </c>
       <c r="AB5" s="3">
         <f t="shared" si="2"/>
-        <v>1593.9422846167452</v>
+        <v>1551.3615276079277</v>
       </c>
       <c r="AC5" s="3">
         <f t="shared" si="2"/>
-        <v>1681.609110270666</v>
+        <v>1636.6864116263637</v>
       </c>
       <c r="AD5" s="3">
         <f>AC5*1.0035</f>
-        <v>1687.4947421566135</v>
+        <v>1642.4148140670561</v>
       </c>
       <c r="AE5" s="3">
         <f>AD5</f>
-        <v>1687.4947421566135</v>
+        <v>1642.4148140670561</v>
       </c>
       <c r="AF5" s="3">
         <v>1500</v>
@@ -2269,40 +2269,40 @@
         <v>408</v>
       </c>
       <c r="W6" s="3">
-        <f t="shared" ref="W6:AA6" si="3">V6*1.02</f>
-        <v>416.16</v>
+        <f>316+162</f>
+        <v>478</v>
       </c>
       <c r="X6" s="3">
-        <f t="shared" si="3"/>
-        <v>424.48320000000001</v>
+        <f t="shared" ref="W6:AA6" si="3">W6*1.02</f>
+        <v>487.56</v>
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="3"/>
-        <v>432.97286400000002</v>
+        <v>497.31119999999999</v>
       </c>
       <c r="Z6" s="3">
         <f t="shared" si="3"/>
-        <v>441.63232128000004</v>
+        <v>507.25742400000001</v>
       </c>
       <c r="AA6" s="3">
         <f t="shared" si="3"/>
-        <v>450.46496770560003</v>
+        <v>517.40257248</v>
       </c>
       <c r="AB6" s="3">
         <f>AA6*1.0198</f>
-        <v>459.38417406617094</v>
+        <v>527.64714341510398</v>
       </c>
       <c r="AC6" s="3">
         <f>AB6</f>
-        <v>459.38417406617094</v>
+        <v>527.64714341510398</v>
       </c>
       <c r="AD6" s="3">
         <f t="shared" ref="AD6:AE6" si="4">AC6</f>
-        <v>459.38417406617094</v>
+        <v>527.64714341510398</v>
       </c>
       <c r="AE6" s="3">
         <f t="shared" si="4"/>
-        <v>459.38417406617094</v>
+        <v>527.64714341510398</v>
       </c>
       <c r="AF6" s="3">
         <v>650</v>
@@ -2377,40 +2377,40 @@
         <v>723</v>
       </c>
       <c r="W7" s="3">
-        <f t="shared" ref="W7:AA7" si="5">V7*1.05</f>
-        <v>759.15</v>
+        <f>673+74+88</f>
+        <v>835</v>
       </c>
       <c r="X7" s="3">
-        <f t="shared" si="5"/>
-        <v>797.10749999999996</v>
+        <f t="shared" ref="W7:AA7" si="5">W7*1.05</f>
+        <v>876.75</v>
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="5"/>
-        <v>836.96287499999994</v>
+        <v>920.58750000000009</v>
       </c>
       <c r="Z7" s="3">
         <f t="shared" si="5"/>
-        <v>878.81101875000002</v>
+        <v>966.61687500000016</v>
       </c>
       <c r="AA7" s="3">
         <f t="shared" si="5"/>
-        <v>922.75156968750002</v>
+        <v>1014.9477187500003</v>
       </c>
       <c r="AB7" s="3">
         <f>AA7*1.0454</f>
-        <v>964.6444909513126</v>
+        <v>1061.0263451812505</v>
       </c>
       <c r="AC7" s="3">
         <f>AB7</f>
-        <v>964.6444909513126</v>
+        <v>1061.0263451812505</v>
       </c>
       <c r="AD7" s="3">
         <f t="shared" ref="AD7:AE7" si="6">AC7</f>
-        <v>964.6444909513126</v>
+        <v>1061.0263451812505</v>
       </c>
       <c r="AE7" s="3">
         <f t="shared" si="6"/>
-        <v>964.6444909513126</v>
+        <v>1061.0263451812505</v>
       </c>
       <c r="AF7" s="3">
         <v>1125</v>
@@ -2497,39 +2497,39 @@
       </c>
       <c r="W8" s="25">
         <f t="shared" ref="W8" si="15">+SUM(W4:W7)</f>
-        <v>5139.84</v>
+        <v>5214</v>
       </c>
       <c r="X8" s="25">
         <f t="shared" ref="X8" si="16">+SUM(X4:X7)</f>
-        <v>5335.5461000000005</v>
+        <v>5412.0150000000003</v>
       </c>
       <c r="Y8" s="25">
         <f t="shared" ref="Y8" si="17">+SUM(Y4:Y7)</f>
-        <v>5539.4762235000007</v>
+        <v>5618.3419749999994</v>
       </c>
       <c r="Z8" s="25">
         <f t="shared" ref="Z8" si="18">+SUM(Z4:Z7)</f>
-        <v>5752.0056148024996</v>
+        <v>5833.3598891250003</v>
       </c>
       <c r="AA8" s="25">
         <f t="shared" ref="AA8" si="19">+SUM(AA4:AA7)</f>
-        <v>5969.1784653927953</v>
+        <v>6053.1658532987758</v>
       </c>
       <c r="AB8" s="25">
         <f t="shared" ref="AB8" si="20">+SUM(AB4:AB7)</f>
-        <v>6103.0871102246874</v>
+        <v>6190.3657179811826</v>
       </c>
       <c r="AC8" s="25">
         <f t="shared" ref="AC8" si="21">+SUM(AC4:AC7)</f>
-        <v>6190.753935878608</v>
+        <v>6275.6906019996195</v>
       </c>
       <c r="AD8" s="25">
         <f t="shared" ref="AD8" si="22">+SUM(AD4:AD7)</f>
-        <v>6196.639567764556</v>
+        <v>6281.4190044403103</v>
       </c>
       <c r="AE8" s="25">
         <f t="shared" ref="AE8" si="23">+SUM(AE4:AE7)</f>
-        <v>6196.639567764556</v>
+        <v>6281.4190044403103</v>
       </c>
       <c r="AF8" s="25">
         <f t="shared" ref="AF8" si="24">+SUM(AF4:AF7)</f>
@@ -3139,40 +3139,39 @@
         <v>34604</v>
       </c>
       <c r="W15" s="3">
-        <f t="shared" ref="W15:AC15" si="48">W4*W9</f>
-        <v>40189.987408932837</v>
+        <v>36585</v>
       </c>
       <c r="X15" s="3">
-        <f t="shared" si="48"/>
-        <v>43465.471382760865</v>
+        <f t="shared" ref="W15:AC15" si="48">X4*X9</f>
+        <v>42975.387286767691</v>
       </c>
       <c r="Y15" s="3">
         <f t="shared" si="48"/>
-        <v>47007.907300455874</v>
+        <v>46477.881350639254</v>
       </c>
       <c r="Z15" s="3">
         <f t="shared" si="48"/>
-        <v>50839.05174544303</v>
+        <v>50265.828680716353</v>
       </c>
       <c r="AA15" s="3">
         <f t="shared" si="48"/>
-        <v>54905.0320064142</v>
+        <v>54285.963994028352</v>
       </c>
       <c r="AB15" s="3">
         <f t="shared" si="48"/>
-        <v>57650.283606734913</v>
+        <v>57000.262193729774</v>
       </c>
       <c r="AC15" s="3">
         <f t="shared" si="48"/>
-        <v>60532.797787071664</v>
+        <v>59850.275303416267</v>
       </c>
       <c r="AD15" s="3">
         <f>AD4*AD9</f>
-        <v>63559.437676425252</v>
+        <v>62842.789068587081</v>
       </c>
       <c r="AE15" s="3">
         <f>AE4*AE9</f>
-        <v>66737.409560246524</v>
+        <v>65984.928522016446</v>
       </c>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.2">
@@ -3238,40 +3237,39 @@
         <v>9386</v>
       </c>
       <c r="W16" s="3">
-        <f t="shared" ref="W16:AD16" si="49">W5*W10</f>
-        <v>11711.468970924025</v>
+        <v>10172</v>
       </c>
       <c r="X16" s="3">
-        <f t="shared" si="49"/>
-        <v>12602.711759611344</v>
+        <f t="shared" ref="W16:AD16" si="49">X5*X10</f>
+        <v>12266.041472194251</v>
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="49"/>
-        <v>13561.778124517765</v>
+        <v>13199.487228228232</v>
       </c>
       <c r="Z16" s="3">
         <f t="shared" si="49"/>
-        <v>14593.829439793568</v>
+        <v>14203.9682062964</v>
       </c>
       <c r="AA16" s="3">
         <f t="shared" si="49"/>
-        <v>15704.419860161859</v>
+        <v>15284.890186795557</v>
       </c>
       <c r="AB16" s="3">
         <f t="shared" si="49"/>
-        <v>16899.526211520177</v>
+        <v>16448.070330010698</v>
       </c>
       <c r="AC16" s="3">
         <f t="shared" si="49"/>
-        <v>18185.58015621686</v>
+        <v>17699.768482124513</v>
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="49"/>
-        <v>18614.214280498894</v>
+        <v>18116.952025248189</v>
       </c>
       <c r="AE16" s="3">
         <f t="shared" ref="AE16" si="50">AE5*AE10</f>
-        <v>18986.498566108872</v>
+        <v>18479.291065753154</v>
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.2">
@@ -3337,40 +3335,39 @@
         <v>5189</v>
       </c>
       <c r="W17" s="3">
-        <f t="shared" ref="W17:AD17" si="51">W6*W11</f>
-        <v>3784.7212394628978</v>
+        <v>5629</v>
       </c>
       <c r="X17" s="3">
-        <f t="shared" si="51"/>
-        <v>3899.0198208946772</v>
+        <f t="shared" ref="W17:AD17" si="51">X6*X11</f>
+        <v>4478.4012744801412</v>
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="51"/>
-        <v>4016.7702194856965</v>
+        <v>4613.6489929694417</v>
       </c>
       <c r="Z17" s="3">
         <f t="shared" si="51"/>
-        <v>4138.0766801141644</v>
+        <v>4752.9811925571194</v>
       </c>
       <c r="AA17" s="3">
         <f t="shared" si="51"/>
-        <v>4263.0465958536133</v>
+        <v>4896.5212245723442</v>
       </c>
       <c r="AB17" s="3">
         <f t="shared" si="51"/>
-        <v>4390.9294676360305</v>
+        <v>5043.4070682670654</v>
       </c>
       <c r="AC17" s="3">
         <f t="shared" si="51"/>
-        <v>4434.8387623123908</v>
+        <v>5093.8411389497369</v>
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="51"/>
-        <v>4479.1871499355148</v>
+        <v>5144.7795503392344</v>
       </c>
       <c r="AE17" s="3">
         <f t="shared" ref="AE17" si="52">AE6*AE11</f>
-        <v>4523.9790214348695</v>
+        <v>5196.2273458426262</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
@@ -3435,40 +3432,39 @@
         <v>7181</v>
       </c>
       <c r="W18" s="3">
-        <f t="shared" ref="W18:AD18" si="53">W7*W12</f>
-        <v>6656.9109076961404</v>
+        <v>7986</v>
       </c>
       <c r="X18" s="3">
-        <f t="shared" si="53"/>
-        <v>7129.551582142567</v>
+        <f t="shared" ref="W18:AD18" si="53">X7*X12</f>
+        <v>7841.8962933399771</v>
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="53"/>
-        <v>7635.7497444746896</v>
+        <v>8398.6709301671162</v>
       </c>
       <c r="Z18" s="3">
         <f t="shared" si="53"/>
-        <v>8177.8879763323939</v>
+        <v>8994.9765662089831</v>
       </c>
       <c r="AA18" s="3">
         <f t="shared" si="53"/>
-        <v>8758.5180226519951</v>
+        <v>9633.6199024098223</v>
       </c>
       <c r="AB18" s="3">
         <f t="shared" si="53"/>
-        <v>9339.2778356980052</v>
+        <v>10272.405970898815</v>
       </c>
       <c r="AC18" s="3">
         <f t="shared" si="53"/>
-        <v>9526.0633924119647</v>
+        <v>10477.854090316792</v>
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="53"/>
-        <v>9716.5846602602032</v>
+        <v>10687.411172123129</v>
       </c>
       <c r="AE18" s="3">
         <f t="shared" ref="AE18" si="54">AE7*AE12</f>
-        <v>9910.916353465409</v>
+        <v>10901.159395565592</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.2">
@@ -3541,40 +3537,39 @@
         <v>56360</v>
       </c>
       <c r="W19" s="25">
-        <f t="shared" si="55"/>
-        <v>62343.088527015898</v>
+        <v>60372</v>
       </c>
       <c r="X19" s="25">
         <f t="shared" ref="X19:AD19" si="56">SUM(X15:X18)</f>
-        <v>67096.754545409451</v>
+        <v>67561.726326782067</v>
       </c>
       <c r="Y19" s="25">
         <f t="shared" si="56"/>
-        <v>72222.205388934017</v>
+        <v>72689.68850200405</v>
       </c>
       <c r="Z19" s="25">
         <f t="shared" si="56"/>
-        <v>77748.845841683156</v>
+        <v>78217.754645778841</v>
       </c>
       <c r="AA19" s="25">
         <f t="shared" si="56"/>
-        <v>83631.016485081665</v>
+        <v>84100.995307806064</v>
       </c>
       <c r="AB19" s="25">
         <f t="shared" si="56"/>
-        <v>88280.017121589131</v>
+        <v>88764.145562906371</v>
       </c>
       <c r="AC19" s="25">
         <f t="shared" si="56"/>
-        <v>92679.280098012867</v>
+        <v>93121.739014807303</v>
       </c>
       <c r="AD19" s="25">
         <f t="shared" si="56"/>
-        <v>96369.423767119879</v>
+        <v>96791.931816297641</v>
       </c>
       <c r="AE19" s="25">
         <f>SUM(AE15:AE18)</f>
-        <v>100158.80350125568</v>
+        <v>100561.6063291778</v>
       </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.2">
@@ -4573,7 +4568,7 @@
       </c>
       <c r="W34" s="28">
         <f t="shared" si="73"/>
-        <v>3.0000000000000027E-2</v>
+        <v>1.8386491557223161E-2</v>
       </c>
       <c r="X34" s="28">
         <f t="shared" si="73"/>
@@ -4677,7 +4672,7 @@
       </c>
       <c r="W35" s="27">
         <f t="shared" si="74"/>
-        <v>5.4999999999999938E-2</v>
+        <v>2.6816608996539815E-2</v>
       </c>
       <c r="X35" s="27">
         <f t="shared" si="74"/>
@@ -4781,7 +4776,7 @@
       </c>
       <c r="W36" s="27">
         <f t="shared" si="75"/>
-        <v>2.0000000000000018E-2</v>
+        <v>0.17156862745098045</v>
       </c>
       <c r="X36" s="27">
         <f t="shared" si="75"/>
@@ -4885,7 +4880,7 @@
       </c>
       <c r="W37" s="27">
         <f t="shared" si="76"/>
-        <v>5.0000000000000044E-2</v>
+        <v>0.15491009681881041</v>
       </c>
       <c r="X37" s="27">
         <f t="shared" si="76"/>
@@ -4988,39 +4983,39 @@
       </c>
       <c r="W38" s="27">
         <f t="shared" si="78"/>
-        <v>0.10615841957089955</v>
+        <v>7.1185237757274589E-2</v>
       </c>
       <c r="X38" s="27">
         <f t="shared" si="78"/>
-        <v>7.625008851355819E-2</v>
+        <v>0.11909041156135403</v>
       </c>
       <c r="Y38" s="27">
         <f t="shared" si="78"/>
-        <v>7.6388953210185129E-2</v>
+        <v>7.5900401810621076E-2</v>
       </c>
       <c r="Z38" s="27">
         <f t="shared" si="78"/>
-        <v>7.6522731796776933E-2</v>
+        <v>7.6050210940474594E-2</v>
       </c>
       <c r="AA38" s="27">
         <f t="shared" si="78"/>
-        <v>7.5656050964102217E-2</v>
+        <v>7.5216179353017498E-2</v>
       </c>
       <c r="AB38" s="27">
         <f t="shared" si="78"/>
-        <v>5.5589431193111993E-2</v>
+        <v>5.544702815981406E-2</v>
       </c>
       <c r="AC38" s="27">
         <f t="shared" si="78"/>
-        <v>4.9833055314937091E-2</v>
+        <v>4.9091819948998916E-2</v>
       </c>
       <c r="AD38" s="27">
         <f t="shared" si="78"/>
-        <v>3.9816274632307191E-2</v>
+        <v>3.9412846455828543E-2</v>
       </c>
       <c r="AE38" s="27">
         <f t="shared" si="78"/>
-        <v>3.932139039549476E-2</v>
+        <v>3.8946164645568437E-2</v>
       </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.2">
@@ -15751,7 +15746,7 @@
       </c>
       <c r="J51" s="27">
         <f>Main!I5/(Main!I7+Main!I5)</f>
-        <v>0.98353479157651647</v>
+        <v>0.98423273776058717</v>
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.2">
@@ -15760,7 +15755,7 @@
       </c>
       <c r="J52" s="31">
         <f>1-J51</f>
-        <v>1.6465208423483535E-2</v>
+        <v>1.5767262239412827E-2</v>
       </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.2">
@@ -15769,7 +15764,7 @@
       </c>
       <c r="J53" s="35">
         <f>(J51*J50)+(J52*J49*(1-27%))</f>
-        <v>8.2519926119479212E-2</v>
+        <v>8.2554603575634766E-2</v>
       </c>
     </row>
   </sheetData>
@@ -15870,21 +15865,21 @@
       </c>
       <c r="M5" s="40">
         <f>Q5+1%</f>
-        <v>9.2519926119479207E-2</v>
+        <v>9.2554603575634761E-2</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>178</v>
       </c>
       <c r="Q5" s="40">
         <f>Ratios!J53</f>
-        <v>8.2519926119479212E-2</v>
+        <v>8.2554603575634766E-2</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>178</v>
       </c>
       <c r="U5" s="40">
         <f>Q5-1%</f>
-        <v>7.2519926119479217E-2</v>
+        <v>7.2554603575634771E-2</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
@@ -15941,14 +15936,14 @@
       </c>
       <c r="D9" s="42">
         <f>CHOOSE(D7,M5,Q5,U5)</f>
-        <v>8.2519926119479212E-2</v>
+        <v>8.2554603575634766E-2</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>209</v>
       </c>
       <c r="H9" s="39">
         <f>Main!I3</f>
-        <v>152.19999999999999</v>
+        <v>159.05000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
@@ -15964,7 +15959,7 @@
       </c>
       <c r="H10" s="43">
         <f ca="1">V67</f>
-        <v>93.570985767575579</v>
+        <v>95.212756614336314</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>210</v>
@@ -15991,28 +15986,28 @@
       </c>
       <c r="H11" s="44">
         <f ca="1">H10/H9-1</f>
-        <v>-0.38521034318281477</v>
+        <v>-0.40136588107930649</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>211</v>
       </c>
       <c r="M11" s="44">
         <f>M10/H9-1</f>
-        <v>-0.72010512483574241</v>
+        <v>-0.73215969820811067</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>211</v>
       </c>
       <c r="Q11" s="44">
         <f>Q10/H9-1</f>
-        <v>-0.39684625492772663</v>
+        <v>-0.42282301163156244</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>211</v>
       </c>
       <c r="U11" s="44">
         <f>U10/H9-1</f>
-        <v>0.27582128777923809</v>
+        <v>0.22087393901288888</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -16183,39 +16178,39 @@
       </c>
       <c r="N18" s="47">
         <f ca="1">M18*(1+N19)</f>
-        <v>62343.088527015905</v>
+        <v>60372</v>
       </c>
       <c r="O18" s="47">
         <f t="shared" ref="O18:R18" ca="1" si="0">N18*(1+O19)</f>
-        <v>67096.754545409465</v>
+        <v>67561.726326782067</v>
       </c>
       <c r="P18" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>72222.205388934031</v>
+        <v>72689.688502004035</v>
       </c>
       <c r="Q18" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>77748.845841683171</v>
+        <v>78217.754645778827</v>
       </c>
       <c r="R18" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>83631.01648508168</v>
+        <v>84100.99530780605</v>
       </c>
       <c r="S18" s="47">
         <f t="shared" ref="S18" ca="1" si="1">R18*(1+S19)</f>
-        <v>88280.017121589146</v>
+        <v>88764.145562906357</v>
       </c>
       <c r="T18" s="47">
         <f t="shared" ref="T18" ca="1" si="2">S18*(1+T19)</f>
-        <v>92679.280098012896</v>
+        <v>93121.739014807288</v>
       </c>
       <c r="U18" s="47">
         <f t="shared" ref="U18:V18" ca="1" si="3">T18*(1+U19)</f>
-        <v>96369.423767119893</v>
+        <v>96791.931816297627</v>
       </c>
       <c r="V18" s="47">
         <f t="shared" ca="1" si="3"/>
-        <v>100158.80350125568</v>
+        <v>100561.60632917778</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.2">
@@ -16248,39 +16243,39 @@
       </c>
       <c r="N19" s="27" cm="1">
         <f t="array" aca="1" ref="N19" ca="1">OFFSET(N19,$D$4,,)</f>
-        <v>0.10615841957089955</v>
+        <v>7.1185237757274589E-2</v>
       </c>
       <c r="O19" s="27" cm="1">
         <f t="array" aca="1" ref="O19" ca="1">OFFSET(O19,$D$4,,)</f>
-        <v>7.625008851355819E-2</v>
+        <v>0.11909041156135403</v>
       </c>
       <c r="P19" s="27" cm="1">
         <f t="array" aca="1" ref="P19" ca="1">OFFSET(P19,$D$4,,)</f>
-        <v>7.6388953210185129E-2</v>
+        <v>7.5900401810621076E-2</v>
       </c>
       <c r="Q19" s="27" cm="1">
         <f t="array" aca="1" ref="Q19" ca="1">OFFSET(Q19,$D$4,,)</f>
-        <v>7.6522731796776933E-2</v>
+        <v>7.6050210940474594E-2</v>
       </c>
       <c r="R19" s="27" cm="1">
         <f t="array" aca="1" ref="R19" ca="1">OFFSET(R19,$D$4,,)</f>
-        <v>7.5656050964102217E-2</v>
+        <v>7.5216179353017498E-2</v>
       </c>
       <c r="S19" s="27" cm="1">
         <f t="array" aca="1" ref="S19" ca="1">OFFSET(S19,$D$4,,)</f>
-        <v>5.5589431193111993E-2</v>
+        <v>5.544702815981406E-2</v>
       </c>
       <c r="T19" s="27" cm="1">
         <f t="array" aca="1" ref="T19" ca="1">OFFSET(T19,$D$4,,)</f>
-        <v>4.9833055314937091E-2</v>
+        <v>4.9091819948998916E-2</v>
       </c>
       <c r="U19" s="27" cm="1">
         <f t="array" aca="1" ref="U19" ca="1">OFFSET(U19,$D$4,,)</f>
-        <v>3.9816274632307191E-2</v>
+        <v>3.9412846455828543E-2</v>
       </c>
       <c r="V19" s="27" cm="1">
         <f t="array" aca="1" ref="V19" ca="1">OFFSET(V19,$D$4,,)</f>
-        <v>3.932139039549476E-2</v>
+        <v>3.8946164645568437E-2</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.2">
@@ -16298,39 +16293,39 @@
       </c>
       <c r="N20" s="49">
         <f t="shared" ref="N20:V20" si="5">N21-1%</f>
-        <v>9.6158419570899559E-2</v>
+        <v>6.1185237757274587E-2</v>
       </c>
       <c r="O20" s="49">
         <f t="shared" si="5"/>
-        <v>6.6250088513558195E-2</v>
+        <v>0.10909041156135403</v>
       </c>
       <c r="P20" s="49">
         <f t="shared" si="5"/>
-        <v>6.6388953210185134E-2</v>
+        <v>6.5900401810621081E-2</v>
       </c>
       <c r="Q20" s="49">
         <f t="shared" si="5"/>
-        <v>6.6522731796776938E-2</v>
+        <v>6.6050210940474599E-2</v>
       </c>
       <c r="R20" s="49">
         <f t="shared" si="5"/>
-        <v>6.5656050964102222E-2</v>
+        <v>6.5216179353017503E-2</v>
       </c>
       <c r="S20" s="49">
         <f t="shared" si="5"/>
-        <v>4.5589431193111991E-2</v>
+        <v>4.5447028159814058E-2</v>
       </c>
       <c r="T20" s="49">
         <f t="shared" si="5"/>
-        <v>3.9833055314937089E-2</v>
+        <v>3.9091819948998914E-2</v>
       </c>
       <c r="U20" s="49">
         <f t="shared" si="5"/>
-        <v>2.9816274632307189E-2</v>
+        <v>2.9412846455828541E-2</v>
       </c>
       <c r="V20" s="49">
         <f t="shared" si="5"/>
-        <v>2.9321390395494758E-2</v>
+        <v>2.8946164645568435E-2</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.2">
@@ -16348,39 +16343,39 @@
       </c>
       <c r="N21" s="49">
         <f>Model!W38</f>
-        <v>0.10615841957089955</v>
+        <v>7.1185237757274589E-2</v>
       </c>
       <c r="O21" s="49">
         <f>Model!X38</f>
-        <v>7.625008851355819E-2</v>
+        <v>0.11909041156135403</v>
       </c>
       <c r="P21" s="49">
         <f>Model!Y38</f>
-        <v>7.6388953210185129E-2</v>
+        <v>7.5900401810621076E-2</v>
       </c>
       <c r="Q21" s="49">
         <f>Model!Z38</f>
-        <v>7.6522731796776933E-2</v>
+        <v>7.6050210940474594E-2</v>
       </c>
       <c r="R21" s="49">
         <f>Model!AA38</f>
-        <v>7.5656050964102217E-2</v>
+        <v>7.5216179353017498E-2</v>
       </c>
       <c r="S21" s="49">
         <f>Model!AB38</f>
-        <v>5.5589431193111993E-2</v>
+        <v>5.544702815981406E-2</v>
       </c>
       <c r="T21" s="49">
         <f>Model!AC38</f>
-        <v>4.9833055314937091E-2</v>
+        <v>4.9091819948998916E-2</v>
       </c>
       <c r="U21" s="49">
         <f>Model!AD38</f>
-        <v>3.9816274632307191E-2</v>
+        <v>3.9412846455828543E-2</v>
       </c>
       <c r="V21" s="49">
         <f>Model!AE38</f>
-        <v>3.932139039549476E-2</v>
+        <v>3.8946164645568437E-2</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.2">
@@ -16398,39 +16393,39 @@
       </c>
       <c r="N22" s="49">
         <f t="shared" ref="N22:V22" si="6">N21+2%</f>
-        <v>0.12615841957089954</v>
+        <v>9.1185237757274593E-2</v>
       </c>
       <c r="O22" s="49">
         <f t="shared" si="6"/>
-        <v>9.6250088513558194E-2</v>
+        <v>0.13909041156135402</v>
       </c>
       <c r="P22" s="49">
         <f t="shared" si="6"/>
-        <v>9.6388953210185133E-2</v>
+        <v>9.590040181062108E-2</v>
       </c>
       <c r="Q22" s="49">
         <f t="shared" si="6"/>
-        <v>9.6522731796776937E-2</v>
+        <v>9.6050210940474598E-2</v>
       </c>
       <c r="R22" s="49">
         <f t="shared" si="6"/>
-        <v>9.5656050964102221E-2</v>
+        <v>9.5216179353017502E-2</v>
       </c>
       <c r="S22" s="49">
         <f t="shared" si="6"/>
-        <v>7.5589431193111997E-2</v>
+        <v>7.5447028159814064E-2</v>
       </c>
       <c r="T22" s="49">
         <f t="shared" si="6"/>
-        <v>6.9833055314937095E-2</v>
+        <v>6.909181994899892E-2</v>
       </c>
       <c r="U22" s="49">
         <f t="shared" si="6"/>
-        <v>5.9816274632307195E-2</v>
+        <v>5.9412846455828547E-2</v>
       </c>
       <c r="V22" s="49">
         <f t="shared" si="6"/>
-        <v>5.9321390395494764E-2</v>
+        <v>5.8946164645568441E-2</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.2">
@@ -16467,39 +16462,39 @@
       </c>
       <c r="N24" s="47">
         <f ca="1">N25*N18</f>
-        <v>7013.5974592892899</v>
+        <v>6791.85</v>
       </c>
       <c r="O24" s="47">
         <f t="shared" ref="O24:V24" ca="1" si="7">O25*O18</f>
-        <v>7716.1267727220884</v>
+        <v>7769.5985275799385</v>
       </c>
       <c r="P24" s="47">
         <f t="shared" ca="1" si="7"/>
-        <v>8486.1091331997486</v>
+        <v>8541.0383989854745</v>
       </c>
       <c r="Q24" s="47">
         <f t="shared" ca="1" si="7"/>
-        <v>9329.8615010019803</v>
+        <v>9386.1305574934595</v>
       </c>
       <c r="R24" s="47">
         <f t="shared" ca="1" si="7"/>
-        <v>10244.799519422506</v>
+        <v>10302.37192520624</v>
       </c>
       <c r="S24" s="47">
         <f t="shared" ca="1" si="7"/>
-        <v>11035.002140198643</v>
+        <v>11095.518195363295</v>
       </c>
       <c r="T24" s="47">
         <f t="shared" ca="1" si="7"/>
-        <v>11816.608212496645</v>
+        <v>11873.021724387929</v>
       </c>
       <c r="U24" s="47">
         <f t="shared" ca="1" si="7"/>
-        <v>12528.025089725586</v>
+        <v>12582.951136118692</v>
       </c>
       <c r="V24" s="47">
         <f t="shared" ca="1" si="7"/>
-        <v>13020.644455163239</v>
+        <v>13073.008822793112</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.2">
@@ -16730,39 +16725,39 @@
       </c>
       <c r="N30" s="47">
         <f ca="1">N31*N24</f>
-        <v>1823.5353394152155</v>
+        <v>1765.8810000000001</v>
       </c>
       <c r="O30" s="47">
         <f t="shared" ref="O30:U30" ca="1" si="12">O31*O24</f>
-        <v>2006.1929609077431</v>
+        <v>2020.0956171707842</v>
       </c>
       <c r="P30" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>2206.3883746319348</v>
+        <v>2220.6699837362235</v>
       </c>
       <c r="Q30" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>2425.7639902605151</v>
+        <v>2440.3939449482996</v>
       </c>
       <c r="R30" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>2663.6478750498518</v>
+        <v>2678.6167005536226</v>
       </c>
       <c r="S30" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>2869.1005564516472</v>
+        <v>2884.8347307944568</v>
       </c>
       <c r="T30" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>3072.3181352491279</v>
+        <v>3086.9856483408616</v>
       </c>
       <c r="U30" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>2505.6050179451177</v>
+        <v>2516.5902272237386</v>
       </c>
       <c r="V30" s="47">
         <f t="shared" ref="V30" ca="1" si="13">V31*V24</f>
-        <v>2604.128891032648</v>
+        <v>2614.6017645586226</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.2">
@@ -16987,39 +16982,39 @@
       </c>
       <c r="N36" s="52">
         <f t="shared" ca="1" si="16"/>
-        <v>5190.0621198740746</v>
+        <v>5025.9690000000001</v>
       </c>
       <c r="O36" s="52">
         <f t="shared" ca="1" si="16"/>
-        <v>5709.9338118143451</v>
+        <v>5749.5029104091545</v>
       </c>
       <c r="P36" s="52">
         <f t="shared" ca="1" si="16"/>
-        <v>6279.7207585678134</v>
+        <v>6320.3684152492515</v>
       </c>
       <c r="Q36" s="52">
         <f ca="1">Q24-Q30</f>
-        <v>6904.0975107414652</v>
+        <v>6945.7366125451599</v>
       </c>
       <c r="R36" s="52">
         <f ca="1">R24-R30</f>
-        <v>7581.1516443726541</v>
+        <v>7623.7552246526175</v>
       </c>
       <c r="S36" s="52">
         <f t="shared" ref="S36:V36" ca="1" si="17">S24-S30</f>
-        <v>8165.901583746996</v>
+        <v>8210.6834645688377</v>
       </c>
       <c r="T36" s="52">
         <f t="shared" ca="1" si="17"/>
-        <v>8744.2900772475168</v>
+        <v>8786.0360760470667</v>
       </c>
       <c r="U36" s="52">
         <f t="shared" ca="1" si="17"/>
-        <v>10022.420071780469</v>
+        <v>10066.360908894954</v>
       </c>
       <c r="V36" s="53">
         <f t="shared" ca="1" si="17"/>
-        <v>10416.515564130592</v>
+        <v>10458.40705823449</v>
       </c>
     </row>
     <row r="38" spans="2:22" x14ac:dyDescent="0.2">
@@ -17056,39 +17051,39 @@
       </c>
       <c r="N38" s="47">
         <f ca="1">N39*N18</f>
-        <v>1099.7320816165604</v>
+        <v>1064.96208</v>
       </c>
       <c r="O38" s="47">
         <f t="shared" ref="O38:U38" ca="1" si="18">O39*O18</f>
-        <v>1159.9150151774024</v>
+        <v>1167.953075356347</v>
       </c>
       <c r="P38" s="47">
         <f t="shared" ca="1" si="18"/>
-        <v>1223.5493148195885</v>
+        <v>1231.469159410407</v>
       </c>
       <c r="Q38" s="47">
         <f t="shared" ca="1" si="18"/>
-        <v>1290.8350778601048</v>
+        <v>1298.6201957752521</v>
       </c>
       <c r="R38" s="47">
         <f t="shared" ca="1" si="18"/>
-        <v>1360.7246710510012</v>
+        <v>1368.3714964254916</v>
       </c>
       <c r="S38" s="47">
         <f t="shared" ca="1" si="18"/>
-        <v>1407.6392498946575</v>
+        <v>1415.358756734465</v>
       </c>
       <c r="T38" s="47">
         <f t="shared" ca="1" si="18"/>
-        <v>1448.2304902081719</v>
+        <v>1455.144468103646</v>
       </c>
       <c r="U38" s="47">
         <f t="shared" ca="1" si="18"/>
-        <v>1475.7757604744377</v>
+        <v>1482.2459365241423</v>
       </c>
       <c r="V38" s="47">
         <f t="shared" ref="V38" ca="1" si="19">V39*V18</f>
-        <v>1503.1292089824958</v>
+        <v>1509.1742561969713</v>
       </c>
     </row>
     <row r="39" spans="2:22" x14ac:dyDescent="0.2">
@@ -17328,39 +17323,39 @@
       </c>
       <c r="N44" s="47">
         <f ca="1">N45*N18</f>
-        <v>1955.0792562072188</v>
+        <v>1893.2659200000001</v>
       </c>
       <c r="O44" s="47">
         <f t="shared" ref="O44:U44" ca="1" si="26">O45*O18</f>
-        <v>2062.0711380931598</v>
+        <v>2076.3610228557277</v>
       </c>
       <c r="P44" s="47">
         <f t="shared" ca="1" si="26"/>
-        <v>2175.1987819014907</v>
+        <v>2189.2785056185016</v>
       </c>
       <c r="Q44" s="47">
         <f t="shared" ca="1" si="26"/>
-        <v>2294.8179161957423</v>
+        <v>2308.6581258226706</v>
       </c>
       <c r="R44" s="47">
         <f t="shared" ca="1" si="26"/>
-        <v>2419.0660818684464</v>
+        <v>2432.6604380897629</v>
       </c>
       <c r="S44" s="47">
         <f t="shared" ca="1" si="26"/>
-        <v>2502.4697775905024</v>
+        <v>2516.1933453057154</v>
       </c>
       <c r="T44" s="47">
         <f t="shared" ca="1" si="26"/>
-        <v>2574.6319825923056</v>
+        <v>2586.9234988509261</v>
       </c>
       <c r="U44" s="47">
         <f t="shared" ca="1" si="26"/>
-        <v>2623.6013519545554</v>
+        <v>2635.1038871540304</v>
       </c>
       <c r="V44" s="47">
         <f t="shared" ref="V44" ca="1" si="27">V45*V18</f>
-        <v>2672.2297048577702</v>
+        <v>2682.9764554612821</v>
       </c>
     </row>
     <row r="45" spans="2:22" x14ac:dyDescent="0.2">
@@ -17600,39 +17595,39 @@
       </c>
       <c r="N50" s="24">
         <f ca="1">N51*N18</f>
-        <v>-498.74470821612726</v>
+        <v>-482.976</v>
       </c>
       <c r="O50" s="24">
         <f t="shared" ref="O50:U50" ca="1" si="33">O51*O18</f>
-        <v>-536.77403636327574</v>
+        <v>-540.49381061425652</v>
       </c>
       <c r="P50" s="24">
         <f t="shared" ca="1" si="33"/>
-        <v>-577.77764311147223</v>
+        <v>-581.51750801603225</v>
       </c>
       <c r="Q50" s="24">
         <f t="shared" ca="1" si="33"/>
-        <v>-621.99076673346542</v>
+        <v>-625.7420371662306</v>
       </c>
       <c r="R50" s="24">
         <f t="shared" ca="1" si="33"/>
-        <v>-669.0481318806535</v>
+        <v>-672.80796246244836</v>
       </c>
       <c r="S50" s="24">
         <f t="shared" ca="1" si="33"/>
-        <v>-706.24013697271323</v>
+        <v>-710.11316450325091</v>
       </c>
       <c r="T50" s="24">
         <f t="shared" ca="1" si="33"/>
-        <v>-741.43424078410317</v>
+        <v>-744.97391211845832</v>
       </c>
       <c r="U50" s="24">
         <f t="shared" ca="1" si="33"/>
-        <v>-770.95539013695918</v>
+        <v>-774.33545453038107</v>
       </c>
       <c r="V50" s="24">
         <f t="shared" ref="V50" ca="1" si="34">V51*V18</f>
-        <v>-801.27042801004541</v>
+        <v>-804.49285063342222</v>
       </c>
     </row>
     <row r="51" spans="2:22" x14ac:dyDescent="0.2">
@@ -17859,39 +17854,39 @@
       </c>
       <c r="N56" s="57">
         <f t="shared" ca="1" si="38"/>
-        <v>3835.9702370672894</v>
+        <v>3714.6891600000004</v>
       </c>
       <c r="O56" s="57">
         <f t="shared" ca="1" si="38"/>
-        <v>4271.0036525353116</v>
+        <v>4300.6011522955177</v>
       </c>
       <c r="P56" s="57">
         <f t="shared" ca="1" si="38"/>
-        <v>4750.2936483744379</v>
+        <v>4781.0415610251248</v>
       </c>
       <c r="Q56" s="57">
         <f t="shared" ca="1" si="38"/>
-        <v>5278.1239056723625</v>
+        <v>5309.956645331511</v>
       </c>
       <c r="R56" s="57">
         <f t="shared" ca="1" si="38"/>
-        <v>5853.7621016745552</v>
+        <v>5886.6583205258994</v>
       </c>
       <c r="S56" s="57">
         <f t="shared" ca="1" si="38"/>
-        <v>6364.8309190784375</v>
+        <v>6399.735711494337</v>
       </c>
       <c r="T56" s="57">
         <f t="shared" ca="1" si="38"/>
-        <v>6876.4543440792804</v>
+        <v>6909.2831331813286</v>
       </c>
       <c r="U56" s="57">
         <f t="shared" ca="1" si="38"/>
-        <v>8103.6390901633922</v>
+        <v>8139.1675037346868</v>
       </c>
       <c r="V56" s="57">
         <f t="shared" ca="1" si="38"/>
-        <v>8446.144640245273</v>
+        <v>8480.1120083367568</v>
       </c>
     </row>
     <row r="57" spans="2:22" x14ac:dyDescent="0.2">
@@ -17944,43 +17939,43 @@
       </c>
       <c r="M58" s="47">
         <f ca="1">M56/(1+$D$9)^M57</f>
-        <v>3101.1312023360447</v>
+        <v>3101.0318638445292</v>
       </c>
       <c r="N58" s="47">
         <f ca="1">N56/(1+$D$9)^N57</f>
-        <v>3273.4328048830971</v>
+        <v>3169.7342755191817</v>
       </c>
       <c r="O58" s="47">
         <f t="shared" ref="O58:T58" ca="1" si="43">O56/(1+$D$9)^O57</f>
-        <v>3366.8381932658285</v>
+        <v>3389.8441626426197</v>
       </c>
       <c r="P58" s="47">
         <f t="shared" ca="1" si="43"/>
-        <v>3459.2094625864738</v>
+        <v>3481.1543051332278</v>
       </c>
       <c r="Q58" s="47">
         <f t="shared" ca="1" si="43"/>
-        <v>3550.586398607602</v>
+        <v>3571.4281645138731</v>
       </c>
       <c r="R58" s="47">
         <f t="shared" ca="1" si="43"/>
-        <v>3637.639635386663</v>
+        <v>3657.3789550034708</v>
       </c>
       <c r="S58" s="47">
         <f t="shared" ca="1" si="43"/>
-        <v>3653.7226425253521</v>
+        <v>3672.9360004593063</v>
       </c>
       <c r="T58" s="47">
         <f t="shared" ca="1" si="43"/>
-        <v>3646.5096737751719</v>
+        <v>3662.9796023324211</v>
       </c>
       <c r="U58" s="47">
         <f ca="1">U56/(1+$D$9)^U57</f>
-        <v>3969.6936963284761</v>
+        <v>3985.9485219565827</v>
       </c>
       <c r="V58" s="47">
         <f ca="1">V56/(1+$D$9)^V57</f>
-        <v>3822.077792192847</v>
+        <v>3836.2197476418319</v>
       </c>
     </row>
     <row r="59" spans="2:22" x14ac:dyDescent="0.2">
@@ -17993,7 +17988,7 @@
       <c r="Q59" s="47"/>
       <c r="V59" s="47">
         <f ca="1">SUM(M58:V58)</f>
-        <v>35480.841501887553</v>
+        <v>35528.655599047044</v>
       </c>
     </row>
     <row r="60" spans="2:22" x14ac:dyDescent="0.2">
@@ -18006,7 +18001,7 @@
       <c r="Q60" s="47"/>
       <c r="V60" s="47">
         <f ca="1">(V56*(1+D10))/(D9-D10)</f>
-        <v>150509.55104268811</v>
+        <v>151023.79772492961</v>
       </c>
     </row>
     <row r="61" spans="2:22" x14ac:dyDescent="0.2">
@@ -18034,7 +18029,7 @@
       <c r="U61" s="58"/>
       <c r="V61" s="58">
         <f ca="1">V60/(1+D9)^V57</f>
-        <v>68109.088472402553</v>
+        <v>68319.908348695637</v>
       </c>
     </row>
     <row r="62" spans="2:22" x14ac:dyDescent="0.2">
@@ -18062,7 +18057,7 @@
       <c r="U62" s="52"/>
       <c r="V62" s="52">
         <f ca="1">V59+V61</f>
-        <v>103589.92997429011</v>
+        <v>103848.56394774269</v>
       </c>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.2">
@@ -18075,7 +18070,7 @@
       <c r="Q63" s="47"/>
       <c r="V63" s="47">
         <f>Main!I6</f>
-        <v>4640</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.2">
@@ -18116,7 +18111,7 @@
       <c r="Q65" s="47"/>
       <c r="V65" s="47">
         <f ca="1">V62+V63-V64</f>
-        <v>105360.92997429011</v>
+        <v>107209.56394774269</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.2">
@@ -18153,7 +18148,7 @@
       </c>
       <c r="V67" s="32">
         <f ca="1">V65/V66</f>
-        <v>93.570985767575579</v>
+        <v>95.212756614336314</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
@@ -18185,24 +18180,24 @@
       <c r="V71" s="38"/>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="C73" s="63" t="s">
+      <c r="C73" s="62" t="s">
         <v>208</v>
       </c>
-      <c r="D73" s="63"/>
-      <c r="E73" s="63"/>
-      <c r="F73" s="63"/>
-      <c r="G73" s="63"/>
-      <c r="H73" s="63"/>
-      <c r="I73" s="63"/>
-      <c r="J73" s="63"/>
+      <c r="D73" s="62"/>
+      <c r="E73" s="62"/>
+      <c r="F73" s="62"/>
+      <c r="G73" s="62"/>
+      <c r="H73" s="62"/>
+      <c r="I73" s="62"/>
+      <c r="J73" s="62"/>
     </row>
     <row r="74" spans="1:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="64" t="s">
+      <c r="B74" s="63" t="s">
         <v>178</v>
       </c>
       <c r="C74" s="59">
         <f ca="1">V67</f>
-        <v>93.570985767575579</v>
+        <v>95.212756614336314</v>
       </c>
       <c r="D74" s="60">
         <f t="shared" ref="D74:E74" si="44">E74-0.5%</f>
@@ -18233,199 +18228,199 @@
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B75" s="64"/>
+      <c r="B75" s="63"/>
       <c r="C75" s="61">
         <f t="shared" ref="C75:C76" si="46">C76-1%</f>
         <v>4.8759739939255253E-2</v>
       </c>
       <c r="D75" s="33">
         <f t="dataTable" ref="D75:J81" dt2D="1" dtr="1" r1="D10" r2="D9" ca="1"/>
-        <v>160.88452805602199</v>
+        <v>162.85802645579085</v>
       </c>
       <c r="E75" s="33">
-        <v>179.5580448506654</v>
+        <v>181.60664144559232</v>
       </c>
       <c r="F75" s="33">
-        <v>204.72449824142711</v>
+        <v>206.87430529654532</v>
       </c>
       <c r="G75" s="33">
-        <v>240.4830092284011</v>
+        <v>242.77662420498322</v>
       </c>
       <c r="H75" s="33">
-        <v>295.30282442468786</v>
+        <v>297.81690505995726</v>
       </c>
       <c r="I75" s="33">
-        <v>389.96337457548566</v>
+        <v>392.85814603333387</v>
       </c>
       <c r="J75" s="33">
-        <v>592.68712158740607</v>
+        <v>596.39717533426767</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B76" s="64"/>
+      <c r="B76" s="63"/>
       <c r="C76" s="61">
         <f t="shared" si="46"/>
         <v>5.8759739939255255E-2</v>
       </c>
       <c r="D76" s="33">
-        <v>125.17790084732971</v>
+        <v>127.00795742058457</v>
       </c>
       <c r="E76" s="33">
-        <v>135.69212539648987</v>
+        <v>137.56446641438421</v>
       </c>
       <c r="F76" s="33">
-        <v>148.91901637881958</v>
+        <v>150.84455121399264</v>
       </c>
       <c r="G76" s="33">
-        <v>166.0638554869729</v>
+        <v>168.05834072326522</v>
       </c>
       <c r="H76" s="33">
-        <v>189.17009728665462</v>
+        <v>191.25750755014585</v>
       </c>
       <c r="I76" s="33">
-        <v>222.00129477135474</v>
+        <v>224.22074035005156</v>
       </c>
       <c r="J76" s="33">
-        <v>272.33337318031533</v>
+        <v>274.7552363479769</v>
       </c>
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B77" s="64"/>
+      <c r="B77" s="63"/>
       <c r="C77" s="61">
         <f>C78-1%</f>
         <v>6.8759739939255257E-2</v>
       </c>
       <c r="D77" s="33">
-        <v>101.79204561164121</v>
+        <v>103.52827475385968</v>
       </c>
       <c r="E77" s="33">
-        <v>108.31782418400347</v>
+        <v>110.08029766991868</v>
       </c>
       <c r="F77" s="33">
-        <v>116.18195660741009</v>
+        <v>117.97605681677415</v>
       </c>
       <c r="G77" s="33">
-        <v>125.84320492646029</v>
+        <v>127.67615921562692</v>
       </c>
       <c r="H77" s="33">
-        <v>137.99705209529415</v>
+        <v>139.87888480391675</v>
       </c>
       <c r="I77" s="33">
-        <v>153.75100021001882</v>
+        <v>155.69618965444221</v>
       </c>
       <c r="J77" s="33">
-        <v>174.98272668713452</v>
+        <v>177.01330252963461</v>
       </c>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B78" s="64"/>
+      <c r="B78" s="63"/>
       <c r="C78" s="61">
         <v>7.8759739939255252E-2</v>
       </c>
       <c r="D78" s="33">
-        <v>85.339925249749797</v>
+        <v>87.010269587587914</v>
       </c>
       <c r="E78" s="33">
-        <v>89.663936314503502</v>
+        <v>91.351670275859107</v>
       </c>
       <c r="F78" s="33">
-        <v>94.723827263889746</v>
+        <v>96.431910294045537</v>
       </c>
       <c r="G78" s="33">
-        <v>100.72492271967866</v>
+        <v>102.45714000599287</v>
       </c>
       <c r="H78" s="33">
-        <v>107.95676621950246</v>
+        <v>109.71806738971894</v>
       </c>
       <c r="I78" s="33">
-        <v>116.84123460006428</v>
+        <v>118.63826591943564</v>
       </c>
       <c r="J78" s="33">
-        <v>128.01789286489412</v>
+        <v>129.8598727000066</v>
       </c>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B79" s="64"/>
+      <c r="B79" s="63"/>
       <c r="C79" s="61">
         <f>C78+1%</f>
         <v>8.8759739939255247E-2</v>
       </c>
       <c r="D79" s="33">
-        <v>73.171350984824414</v>
+        <v>74.79308868834174</v>
       </c>
       <c r="E79" s="33">
-        <v>76.174507724220334</v>
+        <v>77.808323048326528</v>
       </c>
       <c r="F79" s="33">
-        <v>79.61442538534881</v>
+        <v>81.262074826010775</v>
       </c>
       <c r="G79" s="33">
-        <v>83.593855545180332</v>
+        <v>85.257508828398954</v>
       </c>
       <c r="H79" s="33">
-        <v>88.25052324281333</v>
+        <v>89.932903975359707</v>
       </c>
       <c r="I79" s="33">
-        <v>93.773390758915426</v>
+        <v>95.477982486161821</v>
       </c>
       <c r="J79" s="33">
-        <v>100.42892787559016</v>
+        <v>102.16028578891525</v>
       </c>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B80" s="64"/>
+      <c r="B80" s="63"/>
       <c r="C80" s="61">
         <f t="shared" ref="C80:C81" si="47">C79+1%</f>
         <v>9.8759739939255242E-2</v>
       </c>
       <c r="D80" s="33">
-        <v>63.831183077000262</v>
+        <v>65.415734537253911</v>
       </c>
       <c r="E80" s="33">
-        <v>65.992478560155831</v>
+        <v>67.585721976604631</v>
       </c>
       <c r="F80" s="33">
-        <v>68.428190323103934</v>
+        <v>70.031229299721403</v>
       </c>
       <c r="G80" s="33">
-        <v>71.194124476336214</v>
+        <v>72.808287049280906</v>
       </c>
       <c r="H80" s="33">
-        <v>74.362319335568216</v>
+        <v>75.989223253298377</v>
       </c>
       <c r="I80" s="33">
-        <v>78.027410020010663</v>
+        <v>79.669053619532917</v>
       </c>
       <c r="J80" s="33">
-        <v>82.316242519551594</v>
+        <v>83.975134267004009</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B81" s="64"/>
+      <c r="B81" s="63"/>
       <c r="C81" s="61">
         <f t="shared" si="47"/>
         <v>0.10875973993925524</v>
       </c>
       <c r="D81" s="33">
-        <v>56.454236735660508</v>
+        <v>58.009537708074873</v>
       </c>
       <c r="E81" s="33">
-        <v>58.053635533150896</v>
+        <v>59.615368714578175</v>
       </c>
       <c r="F81" s="33">
-        <v>59.833228504101569</v>
+        <v>61.402118570956709</v>
       </c>
       <c r="G81" s="33">
-        <v>61.825285478909159</v>
+        <v>63.402186885304943</v>
       </c>
       <c r="H81" s="33">
-        <v>64.070270786941791</v>
+        <v>65.656200720028281</v>
       </c>
       <c r="I81" s="33">
-        <v>66.619620685994079</v>
+        <v>68.215803191124209</v>
       </c>
       <c r="J81" s="33">
-        <v>69.539732589280888</v>
+        <v>71.147658738418073</v>
       </c>
     </row>
   </sheetData>

--- a/TJX.xlsx
+++ b/TJX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1525F2-E059-49A4-8200-C010C0411EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849599AB-53C5-4C8D-A44E-AA84DB028CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{03FABE92-8095-40C1-84A9-F723AD2E6BD9}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{03FABE92-8095-40C1-84A9-F723AD2E6BD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1205,14 +1205,14 @@
     <xf numFmtId="2" fontId="13" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="169" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1646,7 +1646,7 @@
       <c r="I4" s="3">
         <v>1126</v>
       </c>
-      <c r="J4" s="64" t="s">
+      <c r="J4" s="62" t="s">
         <v>245</v>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       <c r="I6" s="6">
         <v>6230</v>
       </c>
-      <c r="J6" s="64" t="s">
+      <c r="J6" s="62" t="s">
         <v>245</v>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
         <f>999+1870</f>
         <v>2869</v>
       </c>
-      <c r="J7" s="64" t="s">
+      <c r="J7" s="62" t="s">
         <v>245</v>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
         <v>2714</v>
       </c>
       <c r="X4" s="3">
-        <f t="shared" ref="W4:Y4" si="0">W4*1.03</f>
+        <f t="shared" ref="X4:Y4" si="0">W4*1.03</f>
         <v>2795.42</v>
       </c>
       <c r="Y4" s="3">
@@ -2165,7 +2165,7 @@
         <v>1187</v>
       </c>
       <c r="X5" s="3">
-        <f t="shared" ref="W5:AC5" si="2">W5*1.055</f>
+        <f t="shared" ref="X5:AC5" si="2">W5*1.055</f>
         <v>1252.2849999999999</v>
       </c>
       <c r="Y5" s="3">
@@ -2273,7 +2273,7 @@
         <v>478</v>
       </c>
       <c r="X6" s="3">
-        <f t="shared" ref="W6:AA6" si="3">W6*1.02</f>
+        <f t="shared" ref="X6:AA6" si="3">W6*1.02</f>
         <v>487.56</v>
       </c>
       <c r="Y6" s="3">
@@ -2381,7 +2381,7 @@
         <v>835</v>
       </c>
       <c r="X7" s="3">
-        <f t="shared" ref="W7:AA7" si="5">W7*1.05</f>
+        <f t="shared" ref="X7:AA7" si="5">W7*1.05</f>
         <v>876.75</v>
       </c>
       <c r="Y7" s="3">
@@ -3142,7 +3142,7 @@
         <v>36585</v>
       </c>
       <c r="X15" s="3">
-        <f t="shared" ref="W15:AC15" si="48">X4*X9</f>
+        <f t="shared" ref="X15:AC15" si="48">X4*X9</f>
         <v>42975.387286767691</v>
       </c>
       <c r="Y15" s="3">
@@ -3240,7 +3240,7 @@
         <v>10172</v>
       </c>
       <c r="X16" s="3">
-        <f t="shared" ref="W16:AD16" si="49">X5*X10</f>
+        <f t="shared" ref="X16:AD16" si="49">X5*X10</f>
         <v>12266.041472194251</v>
       </c>
       <c r="Y16" s="3">
@@ -3338,7 +3338,7 @@
         <v>5629</v>
       </c>
       <c r="X17" s="3">
-        <f t="shared" ref="W17:AD17" si="51">X6*X11</f>
+        <f t="shared" ref="X17:AD17" si="51">X6*X11</f>
         <v>4478.4012744801412</v>
       </c>
       <c r="Y17" s="3">
@@ -3435,7 +3435,7 @@
         <v>7986</v>
       </c>
       <c r="X18" s="3">
-        <f t="shared" ref="W18:AD18" si="53">X7*X12</f>
+        <f t="shared" ref="X18:AD18" si="53">X7*X12</f>
         <v>7841.8962933399771</v>
       </c>
       <c r="Y18" s="3">
@@ -3513,7 +3513,7 @@
         <v>38972.934000000001</v>
       </c>
       <c r="Q19" s="25">
-        <f t="shared" ref="Q19:W19" si="55">SUM(Q15:Q18)</f>
+        <f t="shared" ref="Q19:V19" si="55">SUM(Q15:Q18)</f>
         <v>41717</v>
       </c>
       <c r="R19" s="25">
@@ -18180,19 +18180,19 @@
       <c r="V71" s="38"/>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="C73" s="62" t="s">
+      <c r="C73" s="63" t="s">
         <v>208</v>
       </c>
-      <c r="D73" s="62"/>
-      <c r="E73" s="62"/>
-      <c r="F73" s="62"/>
-      <c r="G73" s="62"/>
-      <c r="H73" s="62"/>
-      <c r="I73" s="62"/>
-      <c r="J73" s="62"/>
+      <c r="D73" s="63"/>
+      <c r="E73" s="63"/>
+      <c r="F73" s="63"/>
+      <c r="G73" s="63"/>
+      <c r="H73" s="63"/>
+      <c r="I73" s="63"/>
+      <c r="J73" s="63"/>
     </row>
     <row r="74" spans="1:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="63" t="s">
+      <c r="B74" s="64" t="s">
         <v>178</v>
       </c>
       <c r="C74" s="59">
@@ -18228,7 +18228,7 @@
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B75" s="63"/>
+      <c r="B75" s="64"/>
       <c r="C75" s="61">
         <f t="shared" ref="C75:C76" si="46">C76-1%</f>
         <v>4.8759739939255253E-2</v>
@@ -18257,7 +18257,7 @@
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B76" s="63"/>
+      <c r="B76" s="64"/>
       <c r="C76" s="61">
         <f t="shared" si="46"/>
         <v>5.8759739939255255E-2</v>
@@ -18285,7 +18285,7 @@
       </c>
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B77" s="63"/>
+      <c r="B77" s="64"/>
       <c r="C77" s="61">
         <f>C78-1%</f>
         <v>6.8759739939255257E-2</v>
@@ -18313,7 +18313,7 @@
       </c>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B78" s="63"/>
+      <c r="B78" s="64"/>
       <c r="C78" s="61">
         <v>7.8759739939255252E-2</v>
       </c>
@@ -18340,7 +18340,7 @@
       </c>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B79" s="63"/>
+      <c r="B79" s="64"/>
       <c r="C79" s="61">
         <f>C78+1%</f>
         <v>8.8759739939255247E-2</v>
@@ -18368,7 +18368,7 @@
       </c>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B80" s="63"/>
+      <c r="B80" s="64"/>
       <c r="C80" s="61">
         <f t="shared" ref="C80:C81" si="47">C79+1%</f>
         <v>9.8759739939255242E-2</v>
@@ -18396,7 +18396,7 @@
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B81" s="63"/>
+      <c r="B81" s="64"/>
       <c r="C81" s="61">
         <f t="shared" si="47"/>
         <v>0.10875973993925524</v>

--- a/TJX.xlsx
+++ b/TJX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849599AB-53C5-4C8D-A44E-AA84DB028CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02EFE9C7-9B6C-4BA9-8D7A-11AC8865D2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{03FABE92-8095-40C1-84A9-F723AD2E6BD9}"/>
   </bookViews>
